--- a/entretiens/FPPN_PBC_complementaire_cotisations_20261019.xlsx
+++ b/entretiens/FPPN_PBC_complementaire_cotisations_20261019.xlsx
@@ -834,7 +834,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1" s="35">
+    <row r="11" ht="42" customHeight="1" s="35">
       <c r="B11" s="46">
         <f>56</f>
         <v/>
@@ -868,7 +868,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1" s="35">
+    <row r="12" ht="42" customHeight="1" s="35">
       <c r="B12" s="46">
         <f>+B11+1</f>
         <v/>
@@ -902,7 +902,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1" s="35">
+    <row r="13" ht="42" customHeight="1" s="35">
       <c r="B13" s="46">
         <f>+B12+1</f>
         <v/>
@@ -932,7 +932,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1" s="35">
+    <row r="14" ht="42" customHeight="1" s="35">
       <c r="B14" s="46">
         <f>+B13+1</f>
         <v/>
@@ -962,7 +962,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1" s="35">
+    <row r="15" ht="42" customHeight="1" s="35">
       <c r="B15" s="46">
         <f>+B14+1</f>
         <v/>
@@ -1002,7 +1002,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1" s="35">
+    <row r="18" ht="57" customHeight="1" s="35">
       <c r="B18" s="46">
         <f>+B15+1</f>
         <v/>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="36" customHeight="1" s="35">
+    <row r="19" ht="42" customHeight="1" s="35">
       <c r="B19" s="46">
         <f>+B18+1</f>
         <v/>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="36" customHeight="1" s="35">
+    <row r="20" ht="42" customHeight="1" s="35">
       <c r="B20" s="46">
         <f>+B19+1</f>
         <v/>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="21" customHeight="1" s="35">
+    <row r="21" ht="30" customHeight="1" s="35">
       <c r="B21" s="46">
         <f>+B20+1</f>
         <v/>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="36" customHeight="1" s="35">
+    <row r="22" ht="42" customHeight="1" s="35">
       <c r="B22" s="46">
         <f>+B21+1</f>
         <v/>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="21" customHeight="1" s="35">
+    <row r="25" ht="30" customHeight="1" s="35">
       <c r="B25" s="46">
         <f>+B22+1</f>
         <v/>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="36" customHeight="1" s="35">
+    <row r="26" ht="42" customHeight="1" s="35">
       <c r="B26" s="46">
         <f>+B25+1</f>
         <v/>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="36" customHeight="1" s="35">
+    <row r="29" ht="42" customHeight="1" s="35">
       <c r="B29" s="46">
         <f>+B26+1</f>
         <v/>
@@ -1294,7 +1294,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="36" customHeight="1" s="35">
+    <row r="30" ht="42" customHeight="1" s="35">
       <c r="B30" s="46">
         <f>+B29+1</f>
         <v/>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="36" customHeight="1" s="35">
+    <row r="31" ht="42" customHeight="1" s="35">
       <c r="B31" s="46">
         <f>+B30+1</f>
         <v/>
@@ -1655,7 +1655,7 @@
     <mergeCell ref="C5:M5"/>
     <mergeCell ref="C4:M4"/>
   </mergeCells>
-  <conditionalFormatting sqref="M11:M29">
+  <conditionalFormatting sqref="M11:M31">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="5" text="" percent="0" bottom="0">
       <formula>"Partiellement Reçu"</formula>
     </cfRule>
@@ -1666,7 +1666,7 @@
       <formula>"Reçu"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E11:E29">
+  <conditionalFormatting sqref="E11:E31">
     <cfRule type="cellIs" rank="0" priority="5" equalAverage="0" operator="equal" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
       <formula>"Faible"</formula>
     </cfRule>
